--- a/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,3; 4,99</t>
+          <t>-0,19; 5,32</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 1,05</t>
+          <t>-2,72; 1,06</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 1,25</t>
+          <t>-2,57; 1,31</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 5,74</t>
+          <t>-0,04; 5,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,88</t>
+          <t>-1,61; 2,59</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,75; 2,06</t>
+          <t>-1,58; 2,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 4,45</t>
+          <t>0,48; 4,2</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,4</t>
+          <t>-1,3; 1,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,26</t>
+          <t>-1,38; 1,15</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-46,04; 1220,4</t>
+          <t>-45,14; 1138,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 1293,39</t>
+          <t>-29,91; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-73,22; —</t>
+          <t>-84,12; 586,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-77,89; 525,12</t>
+          <t>-69,91; 581,5</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 745,1</t>
+          <t>9,37; 651,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-72,35; 243,79</t>
+          <t>-69,01; 286,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-67,46; 214,78</t>
+          <t>-70,11; 205,04</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 0,87</t>
+          <t>-2,79; 0,87</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; -0,63</t>
+          <t>-3,78; -0,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,23; 5,03</t>
+          <t>0,19; 5,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,88</t>
+          <t>-1,46; 1,83</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,59; -0,13</t>
+          <t>-2,61; -0,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,01; 5,96</t>
+          <t>2,07; 5,95</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,85</t>
+          <t>-1,62; 0,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,75</t>
+          <t>-2,72; -0,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,77; 4,91</t>
+          <t>1,75; 5,04</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-82,8; 82,03</t>
+          <t>-81,3; 73,56</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -26,79</t>
+          <t>-100,0; -7,99</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,84; 370,55</t>
+          <t>-6,95; 360,3</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-60,41; 200,19</t>
+          <t>-58,95; 206,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 54,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,53; 677,53</t>
+          <t>71,24; 781,22</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,59; 62,04</t>
+          <t>-59,57; 62,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-95,14; -45,79</t>
+          <t>-95,37; -44,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>58,03; 367,35</t>
+          <t>62,1; 362,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,21</t>
+          <t>0,15; 4,21</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,06</t>
+          <t>-0,69; 1,98</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,87</t>
+          <t>0,52; 3,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,01; 2,59</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 1,1</t>
+          <t>-0,56; 1,33</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,32</t>
+          <t>0,15; 2,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,44</t>
+          <t>0,27; 2,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,03</t>
+          <t>-0,45; 0,97</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,55</t>
+          <t>0,61; 2,57</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-10,0; —</t>
+          <t>-40,39; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38,75; —</t>
+          <t>15,64; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 0,23</t>
+          <t>-3,6; 0,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 0,37</t>
+          <t>-3,34; 0,58</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 2,8</t>
+          <t>-2,11; 2,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 4,31</t>
+          <t>-0,07; 4,53</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 3,01</t>
+          <t>-0,81; 3,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,44</t>
+          <t>-1,26; 2,56</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,75</t>
+          <t>-1,26; 1,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,32</t>
+          <t>-1,4; 1,41</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 1,75</t>
+          <t>-1,33; 1,86</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 52,83</t>
+          <t>-100,0; 42,1</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,36</t>
+          <t>-93,64; 83,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-72,2; 205,53</t>
+          <t>-68,66; 236,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-31,83; 711,65</t>
+          <t>-23,6; 863,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-59,3; 580,72</t>
+          <t>-62,59; 597,77</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-70,12; 472,26</t>
+          <t>-67,77; 531,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,96; 139,81</t>
+          <t>-51,87; 151,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,17; 118,7</t>
+          <t>-59,95; 131,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-59,39; 136,07</t>
+          <t>-54,16; 153,28</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0,19; 8,92</t>
+          <t>-0,18; 8,55</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,02; -0,06</t>
+          <t>-5,17; -0,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,32; -0,48</t>
+          <t>-5,54; -0,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 5,03</t>
+          <t>-3,57; 5,03</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,95; -2,58</t>
+          <t>-9,35; -2,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,85; -0,16</t>
+          <t>-7,53; -0,09</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,73</t>
+          <t>-0,87; 5,47</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,19; -2,07</t>
+          <t>-6,08; -2,0</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,8</t>
+          <t>-5,01; -0,68</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,72; 590,98</t>
+          <t>-17,29; 568,69</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 45,22</t>
+          <t>-100,0; 49,56</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 69,76</t>
+          <t>-100,0; 27,01</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-56,7; 161,99</t>
+          <t>-51,61; 163,54</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-84,87; -5,38</t>
+          <t>-86,36; 0,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 181,25</t>
+          <t>-19,16; 191,75</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -54,6</t>
+          <t>-100,0; -59,83</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-84,93; -25,48</t>
+          <t>-84,14; -23,23</t>
         </is>
       </c>
     </row>
@@ -1757,32 +1757,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,54</t>
+          <t>-0,76; 1,18</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,36; 4,96</t>
+          <t>0,4; 5,21</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,84; 4,26</t>
+          <t>0,82; 4,61</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,24</t>
+          <t>-0,34; 2,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 2,86</t>
+          <t>-0,31; 2,77</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,1</t>
+          <t>2,16; 6,14</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,44; 3,0</t>
+          <t>0,49; 3,16</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,74</t>
+          <t>1,86; 4,63</t>
         </is>
       </c>
     </row>
@@ -1898,12 +1898,12 @@
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-8,17; —</t>
+          <t>-17,75; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>142,78; —</t>
+          <t>136,81; —</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,98; 0,68</t>
+          <t>-2,06; 0,6</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 1,23</t>
+          <t>-1,59; 1,37</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,14; 3,84</t>
+          <t>0,03; 3,75</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 1,67</t>
+          <t>-1,25; 1,6</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,79</t>
+          <t>-2,0; 0,91</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,19; 58,69</t>
+          <t>3,11; 62,19</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,84</t>
+          <t>-1,15; 0,87</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 0,52</t>
+          <t>-1,39; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,33; 48,67</t>
+          <t>2,29; 44,9</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-80,52; 80,16</t>
+          <t>-81,34; 72,03</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,04; 134,77</t>
+          <t>-67,63; 156,4</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-4,32; 357,21</t>
+          <t>-13,06; 368,55</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-53,2; 147,57</t>
+          <t>-52,11; 162,95</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,69; 84,03</t>
+          <t>-76,44; 94,51</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>160,71; 7504,29</t>
+          <t>153,24; 8986,46</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-53,57; 73,15</t>
+          <t>-52,93; 79,0</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-63,52; 43,72</t>
+          <t>-62,77; 57,85</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>121,24; 3788,47</t>
+          <t>123,5; 3900,56</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 0,85</t>
+          <t>-1,14; 0,86</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,75</t>
+          <t>-1,25; 0,82</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; -0,06</t>
+          <t>-1,65; 0,07</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 0,79</t>
+          <t>-1,95; 0,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,45; -0,1</t>
+          <t>-2,52; -0,08</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,64; -0,43</t>
+          <t>-2,79; -0,43</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 0,51</t>
+          <t>-1,19; 0,56</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,01</t>
+          <t>-1,55; 0,07</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; -0,36</t>
+          <t>-1,83; -0,43</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-73,52; 164,8</t>
+          <t>-72,93; 160,71</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-80,45; 138,11</t>
+          <t>-77,04; 159,23</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-98,29; 10,06</t>
+          <t>-98,23; 27,53</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 65,91</t>
+          <t>-69,66; 62,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-86,14; -0,96</t>
+          <t>-85,78; 9,94</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-88,51; -25,22</t>
+          <t>-88,73; -20,39</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-61,58; 46,61</t>
+          <t>-60,58; 52,28</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-77,68; 7,54</t>
+          <t>-74,42; 10,27</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-86,11; -30,2</t>
+          <t>-87,73; -37,73</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,73</t>
+          <t>-0,52; 0,74</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 0,05</t>
+          <t>-1,06; 0,05</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,35</t>
+          <t>-0,06; 1,4</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 1,18</t>
+          <t>-0,12; 1,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,17; -0,07</t>
+          <t>-1,19; -0,03</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,09; 23,6</t>
+          <t>1,05; 23,53</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 0,84</t>
+          <t>-0,08; 0,82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-1,0; -0,17</t>
+          <t>-0,95; -0,14</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,86; 13,82</t>
+          <t>0,83; 12,91</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-29,95; 58,24</t>
+          <t>-28,62; 60,0</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-60,36; 7,22</t>
+          <t>-58,53; 6,72</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 102,16</t>
+          <t>-4,75; 110,05</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-8,83; 84,94</t>
+          <t>-6,61; 88,45</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-57,67; -3,42</t>
+          <t>-60,19; -1,67</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>58,71; 1450,72</t>
+          <t>59,89; 1696,84</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 57,42</t>
+          <t>-5,28; 58,05</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-54,1; -12,03</t>
+          <t>-50,91; -7,29</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>53,77; 918,72</t>
+          <t>51,28; 850,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-0,46</t>
+          <t>-0,62</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,45</t>
+          <t>0,48</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,02</t>
+          <t>-0,07</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 5,32</t>
+          <t>-0,19; 5,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 1,06</t>
+          <t>-2,68; 0,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 1,31</t>
+          <t>-2,9; 0,86</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 5,37</t>
+          <t>-0,14; 5,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 2,59</t>
+          <t>-1,49; 2,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 2,16</t>
+          <t>-1,57; 2,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,48; 4,2</t>
+          <t>0,36; 4,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 1,49</t>
+          <t>-1,46; 1,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 1,15</t>
+          <t>-1,55; 1,19</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-35,85%</t>
+          <t>-48,52%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>35,64%</t>
+          <t>37,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-1,55%</t>
+          <t>-5,77%</t>
         </is>
       </c>
     </row>
@@ -783,7 +783,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-45,14; 1138,75</t>
+          <t>-45,36; 1332,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-29,91; —</t>
+          <t>-38,55; 1418,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,12; 586,5</t>
+          <t>-80,08; 664,17</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-69,91; 581,5</t>
+          <t>-67,26; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,37; 651,35</t>
+          <t>9,76; 708,2</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,01; 286,65</t>
+          <t>-71,53; 275,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-70,11; 205,04</t>
+          <t>-68,97; 225,86</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,56</t>
+          <t>2,52</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08</t>
+          <t>4,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>3,33</t>
+          <t>3,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 0,87</t>
+          <t>-2,93; 0,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,78; -0,63</t>
+          <t>-3,88; -0,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,19; 5,24</t>
+          <t>-0,04; 4,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 1,83</t>
+          <t>-1,26; 2,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,61; -0,11</t>
+          <t>-2,77; -0,18</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,07; 5,95</t>
+          <t>2,26; 6,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 0,8</t>
+          <t>-1,53; 0,85</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,72; -0,72</t>
+          <t>-2,75; -0,72</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 5,04</t>
+          <t>1,83; 4,91</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107,72%</t>
+          <t>106,06%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>249,86%</t>
+          <t>252,6%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>166,09%</t>
+          <t>166,61%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-81,3; 73,56</t>
+          <t>-82,44; 85,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -7,99</t>
+          <t>-100,0; -25,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 360,3</t>
+          <t>-4,7; 361,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-58,95; 206,93</t>
+          <t>-57,75; 256,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 37,84</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,24; 781,22</t>
+          <t>59,28; 704,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-59,57; 62,34</t>
+          <t>-59,14; 61,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-95,37; -44,76</t>
+          <t>-94,57; -38,8</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>62,1; 362,7</t>
+          <t>63,79; 362,87</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,98</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,11</t>
+          <t>1,08</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,53</t>
+          <t>1,48</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 4,21</t>
+          <t>0,21; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,98</t>
+          <t>-0,7; 1,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,98</t>
+          <t>0,5; 3,85</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 2,59</t>
+          <t>-0,26; 2,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 1,33</t>
+          <t>-0,56; 1,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,15; 2,24</t>
+          <t>0,11; 2,15</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,57</t>
+          <t>0,28; 2,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 0,97</t>
+          <t>-0,48; 1,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,57</t>
+          <t>0,56; 2,6</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>572,34%</t>
+          <t>558,14%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>402,88%</t>
+          <t>390,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>491,41%</t>
+          <t>476,65%</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1245,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-40,39; —</t>
+          <t>-37,38; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>15,64; —</t>
+          <t>22,78; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-0,0</t>
+          <t>-0,19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,26</t>
+          <t>0,6</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>0,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,12</t>
+          <t>-3,73; 0,14</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 0,58</t>
+          <t>-3,57; 0,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 2,91</t>
+          <t>-2,44; 2,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,53</t>
+          <t>-0,05; 4,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 3,34</t>
+          <t>-0,76; 3,29</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 2,56</t>
+          <t>-0,85; 3,13</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,71</t>
+          <t>-1,22; 1,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 1,41</t>
+          <t>-1,68; 1,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,86</t>
+          <t>-1,27; 1,99</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-0,18%</t>
+          <t>-7,65%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>46,79%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 42,1</t>
+          <t>-92,56; 49,57</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-93,64; 83,21</t>
+          <t>-92,83; 90,85</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-68,66; 236,4</t>
+          <t>-75,29; 199,34</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-23,6; 863,28</t>
+          <t>-19,57; 824,69</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 597,77</t>
+          <t>-58,74; 562,91</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-67,77; 531,11</t>
+          <t>-57,16; 535,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-51,87; 151,38</t>
+          <t>-51,74; 156,03</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-59,95; 131,03</t>
+          <t>-66,81; 113,27</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-54,16; 153,28</t>
+          <t>-52,86; 165,73</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-2,37</t>
+          <t>-2,42</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-3,06</t>
+          <t>-2,61</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,6</t>
+          <t>-2,48</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 8,55</t>
+          <t>-0,35; 8,59</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,17; -0,03</t>
+          <t>-5,22; -0,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,54; -0,33</t>
+          <t>-5,37; -0,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 5,03</t>
+          <t>-4,12; 4,87</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-9,35; -2,51</t>
+          <t>-9,03; -2,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,53; -0,09</t>
+          <t>-6,44; 0,38</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 5,47</t>
+          <t>-0,61; 5,41</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,08; -2,0</t>
+          <t>-5,85; -1,97</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,01; -0,68</t>
+          <t>-5,07; -0,81</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-78,27%</t>
+          <t>-79,89%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-60,11%</t>
+          <t>-51,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-63,89%</t>
+          <t>-60,84%</t>
         </is>
       </c>
     </row>
@@ -1647,22 +1647,22 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-17,29; 568,69</t>
+          <t>-20,01; 547,15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 49,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,01</t>
+          <t>-100,0; 29,87</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-51,61; 163,54</t>
+          <t>-59,07; 168,6</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-86,36; 0,03</t>
+          <t>-80,94; 19,55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,16; 191,75</t>
+          <t>-15,47; 181,85</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -59,83</t>
+          <t>-100,0; -60,52</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-84,14; -23,23</t>
+          <t>-82,17; -21,32</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,56</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,84</t>
+          <t>3,75</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>3,09</t>
+          <t>3,15</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 1,18</t>
+          <t>-0,76; 1,16</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,4; 5,21</t>
+          <t>0,42; 4,85</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,61</t>
+          <t>0,89; 4,71</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,58</t>
+          <t>-0,35; 2,58</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,31; 2,77</t>
+          <t>-0,02; 3,14</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,16; 6,14</t>
+          <t>1,97; 6,07</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,32</t>
+          <t>-0,35; 1,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,49; 3,16</t>
+          <t>0,38; 3,03</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1,86; 4,63</t>
+          <t>1,83; 4,65</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>629,44%</t>
+          <t>680,05%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1119,91%</t>
+          <t>1094,93%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>859,04%</t>
+          <t>876,31%</t>
         </is>
       </c>
     </row>
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-17,75; —</t>
+          <t>-2,95; —</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>136,81; —</t>
+          <t>157,61; —</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1,82</t>
+          <t>2,48</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,52</t>
+          <t>4,54</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>16,06</t>
+          <t>3,54</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,6</t>
+          <t>-1,97; 0,67</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 1,37</t>
+          <t>-1,74; 1,26</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,03; 3,75</t>
+          <t>0,78; 4,71</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 1,6</t>
+          <t>-1,31; 1,62</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,0; 0,91</t>
+          <t>-1,91; 0,92</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,11; 62,19</t>
+          <t>2,74; 6,43</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,87</t>
+          <t>-1,19; 0,75</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,66</t>
+          <t>-1,26; 0,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>2,29; 44,9</t>
+          <t>2,27; 4,95</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>108,84%</t>
+          <t>148,51%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1508,14%</t>
+          <t>258,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>936,91%</t>
+          <t>206,77%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-81,34; 72,03</t>
+          <t>-78,12; 106,51</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-67,63; 156,4</t>
+          <t>-75,9; 130,57</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-13,06; 368,55</t>
+          <t>17,37; 454,2</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,11; 162,95</t>
+          <t>-55,48; 153,06</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-76,44; 94,51</t>
+          <t>-76,26; 105,25</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>153,24; 8986,46</t>
+          <t>91,96; 624,27</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-52,93; 79,0</t>
+          <t>-54,13; 70,92</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,77; 57,85</t>
+          <t>-59,64; 52,98</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>123,5; 3900,56</t>
+          <t>88,62; 408,35</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-0,75</t>
+          <t>-0,44</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>-1,4</t>
+          <t>-1,35</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-1,1</t>
+          <t>-0,91</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 0,86</t>
+          <t>-1,23; 0,81</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 0,82</t>
+          <t>-1,29; 0,8</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 0,07</t>
+          <t>-1,42; 0,58</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 0,74</t>
+          <t>-2,1; 0,63</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-2,52; -0,08</t>
+          <t>-2,74; -0,19</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-2,79; -0,43</t>
+          <t>-2,68; -0,38</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,56</t>
+          <t>-1,23; 0,48</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,07</t>
+          <t>-1,57; 0,01</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-1,83; -0,43</t>
+          <t>-1,7; -0,18</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-68,3%</t>
+          <t>-40,68%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>-68,54%</t>
+          <t>-66,1%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-69,9%</t>
+          <t>-57,55%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-72,93; 160,71</t>
+          <t>-74,14; 146,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-77,04; 159,23</t>
+          <t>-78,81; 157,65</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-98,23; 27,53</t>
+          <t>-89,31; 193,29</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-69,66; 62,42</t>
+          <t>-71,48; 51,42</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-85,78; 9,94</t>
+          <t>-87,49; 4,65</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-88,73; -20,39</t>
+          <t>-86,5; -23,1</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-60,58; 52,28</t>
+          <t>-59,75; 51,11</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-74,42; 10,27</t>
+          <t>-74,59; 9,5</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-87,73; -37,73</t>
+          <t>-79,8; -5,52</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0,67</t>
+          <t>0,94</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>6,62</t>
+          <t>1,57</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,75</t>
+          <t>1,27</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 0,74</t>
+          <t>-0,48; 0,78</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 0,05</t>
+          <t>-1,12; 0,08</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,4</t>
+          <t>0,3; 1,67</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 1,22</t>
+          <t>-0,16; 1,16</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-1,19; -0,03</t>
+          <t>-1,19; -0,06</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,05; 23,53</t>
+          <t>0,93; 2,23</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 0,82</t>
+          <t>-0,12; 0,82</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>-0,95; -0,14</t>
+          <t>-0,98; -0,17</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0,83; 12,91</t>
+          <t>0,79; 1,77</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43,33%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>399,6%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>234,06%</t>
+          <t>79,01%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-28,62; 60,0</t>
+          <t>-27,2; 62,78</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-58,53; 6,72</t>
+          <t>-59,67; 9,78</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-4,75; 110,05</t>
+          <t>13,82; 125,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 88,45</t>
+          <t>-8,45; 84,98</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-60,19; -1,67</t>
+          <t>-59,14; -3,13</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>59,89; 1696,84</t>
+          <t>44,78; 162,34</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 58,05</t>
+          <t>-6,74; 58,11</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>-50,91; -7,29</t>
+          <t>-53,75; -12,07</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>51,28; 850,91</t>
+          <t>40,46; 125,23</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P2A_senso_R-Provincia-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas con limitación por discapacidad sensorial</t>
+          <t>Población que convive con personas con alguna limitación por discapacidad sensorial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
